--- a/testcase/DemoQA_TestCase_v1.2.xlsx
+++ b/testcase/DemoQA_TestCase_v1.2.xlsx
@@ -885,7 +885,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -903,6 +903,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1412,16 +1415,16 @@
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="11" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2468,8 +2471,8 @@
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="14.5047619047619" customWidth="1"/>
-    <col min="4" max="4" width="24.8761904761905" customWidth="1"/>
-    <col min="5" max="5" width="31.247619047619" customWidth="1"/>
+    <col min="4" max="4" width="66.2857142857143" customWidth="1"/>
+    <col min="5" max="5" width="69.1428571428571" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" spans="1:5">
@@ -2502,7 +2505,7 @@
       <c r="D2" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="10" t="s">
         <v>20</v>
       </c>
     </row>

--- a/testcase/DemoQA_TestCase_v1.2.xlsx
+++ b/testcase/DemoQA_TestCase_v1.2.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7620" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12300" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="TextBox" sheetId="1" r:id="rId1"/>
@@ -885,7 +885,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -903,9 +903,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1415,16 +1412,16 @@
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>9</v>
       </c>
     </row>
